--- a/dcf/DDOG.xlsx
+++ b/dcf/DDOG.xlsx
@@ -361,77 +361,77 @@
   <commentList>
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B34" authorId="0" shapeId="0">
       <text>
-        <t>builder default — last-year capex +10% unless set to guidance; edits not tracked</t>
+        <t>workbook (synced) — last-year capex +10% unless set to guidance; edits not tracked</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B38" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B41" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B44" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>Opus: 18.6x</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C52" authorId="0" shapeId="0">
@@ -867,7 +867,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>builder defaults (consensus-anchored; no Opus pass)</t>
+          <t>Opus 4.8 — values as of 2026-07-06 (provenance seeded)</t>
         </is>
       </c>
     </row>
@@ -1122,184 +1122,184 @@
     </row>
     <row r="5">
       <c r="A5" s="52" t="n">
-        <v>9</v>
+        <v>15.6</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>38.25736812224982</v>
+        <v>52.01776455614443</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>37.1336112269365</v>
+        <v>50.27589484856817</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>36.06200284738944</v>
+        <v>48.61657860373179</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>35.03984823407418</v>
+        <v>47.03549677635156</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>34.06460457737101</v>
+        <v>45.52857584741884</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>33.1338717634541</v>
+        <v>44.0919727988818</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>32.24538373246151</v>
+        <v>42.722061071568</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="52" t="n">
-        <v>10</v>
+        <v>16.6</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>40.34227667283991</v>
+        <v>54.10267310673452</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>39.12486632112312</v>
+        <v>52.26714994275479</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>37.9642112953201</v>
+        <v>50.51878705166244</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>36.85737074047984</v>
+        <v>48.85301928275723</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>35.80156992131765</v>
+        <v>47.26554119136549</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>34.79419010215526</v>
+        <v>45.75229113758295</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>33.83275908687158</v>
+        <v>44.30943642597808</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="52" t="n">
-        <v>11</v>
+        <v>17.6</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>42.42718522342999</v>
+        <v>56.18758165732461</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>41.11612141530973</v>
+        <v>54.25840503694141</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>39.86641974325075</v>
+        <v>52.4209954995931</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>38.67489324688551</v>
+        <v>50.67054178916289</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>37.53853526526429</v>
+        <v>49.00250653531212</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>36.45450844085643</v>
+        <v>47.41260947628412</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>35.42013444128165</v>
+        <v>45.89681178038814</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="52" t="n">
-        <v>12</v>
+        <v>18.6</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>44.51209377402009</v>
+        <v>58.27249020791469</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>43.10737650949635</v>
+        <v>56.24966013112802</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>41.76862819118141</v>
+        <v>54.32320394752376</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>40.49241575329118</v>
+        <v>52.48806429556855</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>39.27550060921093</v>
+        <v>50.73947187925877</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>38.1148267795576</v>
+        <v>49.07292781498529</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>37.00750979569172</v>
+        <v>47.48418713479821</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
-        <v>13</v>
+        <v>19.6</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>46.59700232461017</v>
+        <v>60.3573987585048</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>45.09863160368297</v>
+        <v>58.24091522531464</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>43.67083663911207</v>
+        <v>56.22541239545444</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>42.30993825969683</v>
+        <v>54.30558680197422</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>41.01246595315757</v>
+        <v>52.47643722320542</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>39.77514511825876</v>
+        <v>50.73324615368645</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>38.5948851501018</v>
+        <v>49.07156248920829</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
-        <v>14</v>
+        <v>20.6</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>48.68191087520027</v>
+        <v>62.44230730909488</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>47.08988669786957</v>
+        <v>60.23217031950124</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>45.57304508704272</v>
+        <v>58.12762084338508</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>44.1274607661025</v>
+        <v>56.12310930837987</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>42.74943129710422</v>
+        <v>54.21340256715206</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>41.43546345695993</v>
+        <v>52.39356449238763</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>40.18226050451187</v>
+        <v>50.65893784361836</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="52" t="n">
-        <v>15</v>
+        <v>21.6</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>50.76681942579037</v>
+        <v>64.52721585968499</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>49.08114179205621</v>
+        <v>62.22342541368788</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>47.4752535349734</v>
+        <v>60.02982929131574</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>45.94498327250816</v>
+        <v>57.94063181478555</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>44.48639664105086</v>
+        <v>55.95036791109869</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>43.09578179566109</v>
+        <v>54.05388283108879</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>41.76963585892194</v>
+        <v>52.24631319802843</v>
       </c>
     </row>
     <row r="13">
@@ -1322,7 +1322,7 @@
         <v>0.1004079153039895</v>
       </c>
       <c r="C14" s="56" t="n">
-        <v>12</v>
+        <v>18.6</v>
       </c>
     </row>
   </sheetData>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.6617187368958019</v>
+        <v>0.6323411555161563</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24369,7 +24369,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>12</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="46">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>40.49241575329118</v>
+        <v>52.48806429556855</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>55.73010518280717</v>
+        <v>71.792995187904</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>29.54222531286092</v>
+        <v>38.33191491035898</v>
       </c>
     </row>
     <row r="59">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>no Opus assumptions file — every input is a builder default</t>
+          <t>seeded 2026-07-06 from the synced assumptions block (pass predates provenance tracking — may already include your edits)</t>
         </is>
       </c>
     </row>
@@ -24798,7 +24798,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -24806,7 +24806,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="31" t="inlineStr"/>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24825,7 +24829,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -24833,7 +24837,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="31" t="inlineStr"/>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24852,7 +24860,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -24860,7 +24868,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="31" t="inlineStr"/>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24879,7 +24891,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -24887,7 +24899,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="31" t="inlineStr"/>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24906,7 +24922,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -24914,7 +24930,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="31" t="inlineStr"/>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24933,7 +24953,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -24941,7 +24961,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr"/>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24960,7 +24984,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -24968,7 +24992,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="31" t="inlineStr"/>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24987,7 +25015,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -24995,7 +25023,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="31" t="inlineStr"/>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25014,7 +25046,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -25022,7 +25054,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="31" t="inlineStr"/>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25041,7 +25077,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -25049,7 +25085,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="31" t="inlineStr"/>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25068,7 +25108,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -25076,7 +25116,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="31" t="inlineStr"/>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25095,7 +25139,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -25103,7 +25147,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr"/>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25122,12 +25170,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>Opus</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18.6x</t>
         </is>
       </c>
       <c r="F20" s="31" t="inlineStr"/>
@@ -25149,7 +25197,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -25157,7 +25205,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="31" t="inlineStr"/>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25176,7 +25228,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">

--- a/dcf/DDOG.xlsx
+++ b/dcf/DDOG.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.08540791530398952</v>
+        <v>0.08543328457994705</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.09040791530398952</v>
+        <v>0.09043328457994705</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.09540791530398951</v>
+        <v>0.09543328457994704</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.1004079153039895</v>
+        <v>0.100433284579947</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.1054079153039895</v>
+        <v>0.1054332845799471</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.1104079153039895</v>
+        <v>0.110433284579947</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.1154079153039895</v>
+        <v>0.115433284579947</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>15.6</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>52.01776455614443</v>
+        <v>45.17347843187125</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>50.27589484856817</v>
+        <v>43.72764620598846</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>48.61657860373179</v>
+        <v>42.35011757168556</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>47.03549677635156</v>
+        <v>41.03732413697129</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>45.52857584741884</v>
+        <v>39.78590020764952</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>44.0919727988818</v>
+        <v>38.59267038868199</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>42.722061071568</v>
+        <v>37.4546379966582</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>16.6</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>54.10267310673452</v>
+        <v>46.89212434333546</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>52.26714994275479</v>
+        <v>45.36909282631417</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>50.51878705166244</v>
+        <v>43.91816224508059</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>48.85301928275723</v>
+        <v>42.53556135016866</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>47.26554119136549</v>
+        <v>41.21773327759789</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>45.75229113758295</v>
+        <v>39.96132242825778</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>44.30943642597808</v>
+        <v>38.76316220597254</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>17.6</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>56.18758165732461</v>
+        <v>48.61077025479965</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>54.25840503694141</v>
+        <v>47.01053944663987</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>52.4209954995931</v>
+        <v>45.4862069184756</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>50.67054178916289</v>
+        <v>44.03379856336601</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>49.00250653531212</v>
+        <v>42.64956634754628</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>47.41260947628412</v>
+        <v>41.32997446783358</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>45.89681178038814</v>
+        <v>40.07168641528688</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>18.6</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>58.27249020791469</v>
+        <v>50.32941616626385</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>56.24966013112802</v>
+        <v>48.65198606696558</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>54.32320394752376</v>
+        <v>47.05425159187062</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>52.48806429556855</v>
+        <v>45.53203577656335</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>50.73947187925877</v>
+        <v>44.08139941749466</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>49.07292781498529</v>
+        <v>42.69862650740937</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>47.48418713479821</v>
+        <v>41.3802106246012</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>19.6</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>60.3573987585048</v>
+        <v>52.04806207772805</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>58.24091522531464</v>
+        <v>50.29343268729129</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>56.22541239545444</v>
+        <v>48.62229626526565</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>54.30558680197422</v>
+        <v>47.03027298976072</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>52.47643722320542</v>
+        <v>45.51323248744303</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>50.73324615368645</v>
+        <v>44.06727854698518</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>49.07156248920829</v>
+        <v>42.68873483391555</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>20.6</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>62.44230730909488</v>
+        <v>53.76670798919225</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>60.23217031950124</v>
+        <v>51.934879307617</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>58.12762084338508</v>
+        <v>50.19034093866066</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>56.12310930837987</v>
+        <v>48.52851020295807</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>54.21340256715206</v>
+        <v>46.94506555739142</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>52.39356449238763</v>
+        <v>45.43593058656096</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>50.65893784361836</v>
+        <v>43.99725904322989</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>21.6</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>64.52721585968499</v>
+        <v>55.48535390065643</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>62.22342541368788</v>
+        <v>53.5763259279427</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>60.02982929131574</v>
+        <v>51.75838561205568</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>57.94063181478555</v>
+        <v>50.02674741615542</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>55.95036791109869</v>
+        <v>48.37689862733981</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>54.05388283108879</v>
+        <v>46.80458262613676</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>52.24631319802843</v>
+        <v>45.3057832525442</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>260.3599853515625</v>
+        <v>268.3099975585938</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.1004079153039895</v>
+        <v>0.100433284579947</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>18.6</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.6323411555161563</v>
+        <v>0.6440950152080194</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>260.3599853515625</v>
+        <v>268.3099975585938</v>
       </c>
     </row>
     <row r="49">
@@ -24414,7 +24414,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>52.48806429556855</v>
+        <v>45.53203577656335</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>71.792995187904</v>
+        <v>60.50256771922329</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>38.33191491035898</v>
+        <v>34.25056843741385</v>
       </c>
     </row>
     <row r="59">
